--- a/sources/devil_step8.xlsx
+++ b/sources/devil_step8.xlsx
@@ -5669,12 +5669,12 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">

--- a/sources/devil_step8.xlsx
+++ b/sources/devil_step8.xlsx
@@ -856,6 +856,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>d45bec05-7204-4250-b59f-10fc5a9777d7</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>d45bec05-7204-4250-b59f-10fc5a9777d7</t>
@@ -918,6 +923,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>17795a91-f2dd-40be-9ae8-c1cac544dbd8</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>17795a91-f2dd-40be-9ae8-c1cac544dbd8</t>
@@ -978,6 +988,11 @@
       <c r="U8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>6cb3e0a1-740e-4fe0-abcb-9e9234259fe0</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -5969,6 +5984,11 @@
       <c r="S68" t="inlineStr">
         <is>
           <t>hhhhmmLhmm</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>f5b8d288-963e-48b0-91a0-9547d3e2d9cf</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">

--- a/sources/devil_step8.xlsx
+++ b/sources/devil_step8.xlsx
@@ -417,37 +417,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB68"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col hidden="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col hidden="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col hidden="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col hidden="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col hidden="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
-    <col hidden="1" min="16" max="16"/>
-    <col width="23" customWidth="1" min="17" max="17"/>
-    <col hidden="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="227" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="38" customWidth="1" min="25" max="25"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col hidden="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col hidden="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col hidden="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col hidden="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col hidden="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
+    <col hidden="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="18" max="18"/>
+    <col hidden="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="227" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
     <col width="38" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="38" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,125 +476,130 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -610,57 +616,57 @@
           <t>1+3</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Bitch Kicks</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Bitch Kicks</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>10,20</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>10,20</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>52821774-399c-4492-a1c1-e2d8fe344952</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>246bf65b-6391-41ee-bd43-82fe8b09b1af</t>
         </is>
@@ -677,57 +683,57 @@
           <t>2+4</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Hip Toss</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Hip Toss</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>5da2bc1b-32ec-4831-84b6-821e0667fd97</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>2b1af555-7b2f-4ae1-a4ad-89a47ab4ddd9</t>
         </is>
@@ -744,62 +750,62 @@
           <t>f,f+1+2</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Stone Head</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Stone Head</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Opponent can tech roll after the throw.</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>bfa1e050-8e4e-4a15-a0a3-8301370aeba2</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>5de7f35a-2ffb-42ab-924a-a31d7fb77f7c</t>
         </is>
@@ -823,50 +829,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Steel Pedal Drop</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Steel Pedal Drop</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>d45bec05-7204-4250-b59f-10fc5a9777d7</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>d45bec05-7204-4250-b59f-10fc5a9777d7</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -890,50 +901,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Skull Smash</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Skull Smash</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>17795a91-f2dd-40be-9ae8-c1cac544dbd8</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>17795a91-f2dd-40be-9ae8-c1cac544dbd8</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -957,50 +973,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Atomic Drop</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Atomic Drop</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>6cb3e0a1-740e-4fe0-abcb-9e9234259fe0</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>6cb3e0a1-740e-4fe0-abcb-9e9234259fe0</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1032,125 +1053,130 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
+      <c r="K11" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K11" s="1" t="inlineStr">
+      <c r="L11" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L11" s="1" t="inlineStr">
+      <c r="M11" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M11" s="1" t="inlineStr">
+      <c r="N11" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N11" s="1" t="inlineStr">
+      <c r="O11" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O11" s="1" t="inlineStr">
+      <c r="P11" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P11" s="1" t="inlineStr">
+      <c r="Q11" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q11" s="1" t="inlineStr">
+      <c r="R11" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R11" s="1" t="inlineStr">
+      <c r="S11" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S11" s="1" t="inlineStr">
+      <c r="T11" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T11" s="1" t="inlineStr">
+      <c r="U11" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U11" s="1" t="inlineStr">
+      <c r="V11" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V11" s="1" t="inlineStr">
+      <c r="W11" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W11" s="1" t="inlineStr">
+      <c r="X11" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X11" s="1" t="inlineStr">
+      <c r="Y11" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y11" s="1" t="inlineStr">
+      <c r="Z11" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z11" s="1" t="inlineStr">
+      <c r="AA11" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA11" s="1" t="inlineStr">
+      <c r="AB11" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB11" s="1" t="inlineStr">
+      <c r="AC11" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1167,77 +1193,77 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>9b0168bf-60d5-41a4-aca8-cc28d123c830</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>d98b18e2-3409-4bdb-8aa4-fb70d6d0c4e9</t>
         </is>
@@ -1254,77 +1280,77 @@
           <t>2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>b27645d0-8d2a-45a1-a671-5a72d672347f</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>96a5b23b-162b-49d1-93e1-ade72045ce60</t>
         </is>
@@ -1341,77 +1367,77 @@
           <t>3</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>7180d196-bebb-4094-bbfc-2a540bb1f0d4</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>bd6fe86f-ec83-4177-bf74-f226bfe0f630</t>
         </is>
@@ -1428,77 +1454,77 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>c2bc4d1b-60c7-4ea6-8693-107a1aaebdd1</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>7355f084-0586-4293-b5f4-4317888c4c2f</t>
         </is>
@@ -1515,77 +1541,77 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>e62d88ce-5d00-4933-893d-a1c22ca54628</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>76527d04-0dae-4412-bc4b-8ef712cb4364</t>
         </is>
@@ -1602,77 +1628,77 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>11eb93fe-b19a-46de-b7d2-53619e9a1b7e</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>9c42d1ac-64b6-45ef-bb5c-6c2473cd8551</t>
         </is>
@@ -1689,77 +1715,77 @@
           <t>f+3</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>5b19b065-fafc-4bd9-aad1-e1426015778e</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>a4ff852a-9e61-49f1-8aa7-2923fb3170b3</t>
         </is>
@@ -1776,77 +1802,77 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>cca7643a-7aef-4f2f-8083-d4096f8b747b</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>7e33912e-8b77-452f-a7fc-ab3497403b67</t>
         </is>
@@ -1863,77 +1889,77 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>5184c592-3de6-454a-8cb3-2299fe1a8f19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>388d2d6d-082a-409b-aa2d-fdc3bffe4878</t>
         </is>
@@ -1950,77 +1976,77 @@
           <t>d+2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>e77637e9-b718-47f8-9771-074c64ec5ce7</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>becfe04b-9fa9-4680-9a64-6d01c29895f6</t>
         </is>
@@ -2037,77 +2063,77 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>c1b1a9d5-783e-41f3-a0ee-6b89aafbf5c5</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>620874a7-0a6c-4b90-b1ef-155d74d1b989</t>
         </is>
@@ -2124,77 +2150,77 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>f9fec094-c6e1-4a6c-a6b7-27a285e3f10f</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>64cdb146-0c2d-4f90-91b3-7bb05ac612a0</t>
         </is>
@@ -2211,77 +2237,77 @@
           <t>FC+1</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>a5eb46be-6f5a-4424-83dd-67e65471d96e</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>310d32dc-2c1a-4d84-8942-49d06e31332b</t>
         </is>
@@ -2298,77 +2324,77 @@
           <t>FC+2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>af611047-c8d5-47e5-b8ad-7f88756390b9</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>8a031735-ec83-41fc-acac-a139337f6ac9</t>
         </is>
@@ -2385,77 +2411,77 @@
           <t>FC+3</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>504cdc15-8245-49b9-8199-722d5d33dba9</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>a0a1ba00-7f52-4605-81a6-71f7d6306096</t>
         </is>
@@ -2472,77 +2498,77 @@
           <t>FC+4</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>402e00a5-e5cb-4e47-985b-48becad4200f</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>0e8113a9-d6cf-4c4e-9109-4e069e6def1c</t>
         </is>
@@ -2559,77 +2585,77 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>10fb267e-58df-442f-8c29-be3050a3fb2e</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>9133bda3-d15c-46f2-8350-b7fd59343813</t>
         </is>
@@ -2646,77 +2672,77 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>+25</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>+25</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>+25</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>+25</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>843c350e-cbf4-477e-9d7f-a572102a552c</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>4ff16aeb-0ff5-45fe-b098-48369fcb9eb3</t>
         </is>
@@ -2733,77 +2759,77 @@
           <t>WS+3</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>482b83d7-e124-44fd-8439-46ccb003514d</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>b7c94067-4374-4729-8a29-373a0bef2cb5</t>
         </is>
@@ -2820,77 +2846,77 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>90a9a787-7795-477f-9a20-5d6b96c20275</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>48f5b8c5-7253-46c6-a599-61568732a26c</t>
         </is>
@@ -2907,77 +2933,77 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>ddec1251-016d-4811-9425-b4d0581698ac</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>55a95c7d-28d4-4015-8cd8-1747e3ebd21f</t>
         </is>
@@ -2994,77 +3020,77 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>+30</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>+30</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>+30</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>+30</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>9e11c97b-18e6-418b-9283-b5f047ca5080</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>182e68cd-688c-4e95-ba1b-01d2bdaadb81</t>
         </is>
@@ -3081,77 +3107,77 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>5c9d340c-40ed-4e59-a4ef-4ecfc7169b72</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>9f1fc4bd-a00f-4f62-863f-cb1988d7d9fa</t>
         </is>
@@ -3168,77 +3194,77 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>7b1977c4-43d4-4e23-b99d-505585bba4d1</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>f7854d62-8e79-4164-9b79-4af53ff33f9f</t>
         </is>
@@ -3270,125 +3296,130 @@
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E38" s="1" t="inlineStr">
+      <c r="F38" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F38" s="1" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G38" s="1" t="inlineStr">
+      <c r="H38" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H38" s="1" t="inlineStr">
+      <c r="I38" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I38" s="1" t="inlineStr">
+      <c r="J38" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J38" s="1" t="inlineStr">
+      <c r="K38" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K38" s="1" t="inlineStr">
+      <c r="L38" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L38" s="1" t="inlineStr">
+      <c r="M38" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M38" s="1" t="inlineStr">
+      <c r="N38" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N38" s="1" t="inlineStr">
+      <c r="O38" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O38" s="1" t="inlineStr">
+      <c r="P38" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P38" s="1" t="inlineStr">
+      <c r="Q38" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q38" s="1" t="inlineStr">
+      <c r="R38" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R38" s="1" t="inlineStr">
+      <c r="S38" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S38" s="1" t="inlineStr">
+      <c r="T38" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T38" s="1" t="inlineStr">
+      <c r="U38" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U38" s="1" t="inlineStr">
+      <c r="V38" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V38" s="1" t="inlineStr">
+      <c r="W38" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W38" s="1" t="inlineStr">
+      <c r="X38" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X38" s="1" t="inlineStr">
+      <c r="Y38" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y38" s="1" t="inlineStr">
+      <c r="Z38" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z38" s="1" t="inlineStr">
+      <c r="AA38" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA38" s="1" t="inlineStr">
+      <c r="AB38" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB38" s="1" t="inlineStr">
+      <c r="AC38" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3405,87 +3436,87 @@
           <t>1&lt;2</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>+1 0</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>+1 0</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>+9 +8</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>+9 +8</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>+9 +8</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>+9 +8</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>5,10</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>5,10</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>ce7c71de-f6c0-43d6-b67d-d5b0eb3949d8</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>f7836f2b-114e-4c30-8bde-1330654c383a</t>
         </is>
@@ -3502,87 +3533,87 @@
           <t>1,1&lt;2</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Shining Fists</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Shining Fists</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>+1 -1 -17</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>+1 -1 -17</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>+9 +9 KD</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>+9 +9 KD</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>+9 +9 KD</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>+9 +9 KD</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>5,8,18</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>5,8,18</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>6a02bf68-ff8e-4938-b770-389f2fe7fe3d</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>5d960be5-4e5a-4831-98fc-d6b642e34955</t>
         </is>
@@ -3599,87 +3630,87 @@
           <t>1&lt;2,2</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Demon Slayer</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Demon Slayer</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>+1 0 -12</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>+1 0 -12</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>+9 +8 +1</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>+9 +8 +1</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>+9 +8 +1</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>+9 +8 +1</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>5,10,18</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>5,10,18</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>53dec2ba-7ae7-42d5-95a2-ca60875764b2</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>09c648f1-c929-4ad1-aa8a-5975ef55cd77</t>
         </is>
@@ -3696,102 +3727,102 @@
           <t>df+1,2</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Twin Pistons</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Twin Pistons</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>-1 -6</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>-1 -6</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>8,15</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>8,15</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>You cannot Tag if Devil is teamed up with Kazuya. Angel and Kazuya cannot be teamed up in the arcade version.</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>18467b48-d3b9-491b-a14e-6b47e1337e3f</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>6a53923d-3180-4f7d-aca5-4ba56540c86a</t>
         </is>
@@ -3808,87 +3839,87 @@
           <t>f,N,d,df+1</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Thunder Godfist</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Thunder Godfist</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>842b6501-8e92-4b4e-94cc-4d4e8a632d58</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>f5189464-4ead-4a7c-a123-a8667e343fce</t>
         </is>
@@ -3905,87 +3936,87 @@
           <t>f,N,d,df+1,3</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>– Mid Kick</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Thunder Godfist – Mid Kick</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>-15 -14</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>24,20</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>5bda96a4-8294-45f2-ad26-85542ccc5874</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>01518c4a-94b2-4c28-8cea-357da4748380</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>842b6501-8e92-4b4e-94cc-4d4e8a632d58</t>
         </is>
@@ -4002,87 +4033,87 @@
           <t>f,N,d,df+1,4</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>– Hell Sweep</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Thunder Godfist – Hell Sweep</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>-15 -20</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>24,12</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>478231cc-56aa-4a8d-bda8-4757fe308929</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>dcb733c3-c1b1-4c07-ad7c-b2427591aad5</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>842b6501-8e92-4b4e-94cc-4d4e8a632d58</t>
         </is>
@@ -4099,92 +4130,92 @@
           <t>f,N,d,df+1,uf</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>– Heaven's Gate</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Thunder Godfist – Heaven's Gate</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>-15 -13</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>24,15</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>throw</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>mthrow</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>Does not work in juggles or on jumping opponents. Damage is in addition to the Thunder Godfist damage.</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>44613e25-d99f-4634-92bc-bd977576074a</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>cb7f54fa-c1fa-4bd0-82a3-f82e8afe4c26</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>842b6501-8e92-4b4e-94cc-4d4e8a632d58</t>
         </is>
@@ -4201,97 +4232,97 @@
           <t>SS+2</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Devil Twister</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Devil Twister</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>ebc17204-e684-473c-838a-862f8fb73435</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>17582cdf-cdba-453d-958b-072bbbf92989</t>
         </is>
@@ -4308,97 +4339,97 @@
           <t>f,f+2</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Devil Fist</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Devil Fist</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>OB</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>Does not hit opponents in the air.</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>cef0ada1-b7b4-4ae1-beee-3240cc984550</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>f30c792d-6fce-4d12-8424-7d96be8e9246</t>
         </is>
@@ -4415,87 +4446,87 @@
           <t>2,2</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Demon Backhand Spin</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Demon Backhand Spin</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>0 -13</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>0 -13</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>+9 -2</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>+9 -2</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>+9 -2</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>+9 -2</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>12,21</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>12,21</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>5ad89c9d-0cf4-4d47-ba6f-f5936714fbc5</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>5f72bad3-9154-4120-973e-b19d2375408a</t>
         </is>
@@ -4512,102 +4543,102 @@
           <t>f,N,d,df+2</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Wind Godfist</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Wind Godfist</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>You cannot Tag if Devil is teamed up with Kazuya. Angel and Kazuya cannot be teamed up in the arcade version.</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>f9d2b9c1-929b-442f-ab95-e30b35cd1b0d</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>6218e15b-f82f-48cf-98c4-002b9ede8c03</t>
         </is>
@@ -4624,87 +4655,87 @@
           <t>f,f+3</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Split Axe Kick</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Split Axe Kick</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>5c2db629-a18d-4d61-ac60-d8d4a70dd1b4</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>7792cdfc-ce6f-45c2-9f19-92142004a167</t>
         </is>
@@ -4728,90 +4759,95 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>f,f,f+3</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>Leaping Slash Kick</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Leaping Slash Kick</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>874e26a7-dfb4-4be5-9a32-53b448cb9de1</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>b066c0a1-f18c-4603-b0b7-b84ea229195e</t>
         </is>
@@ -4828,92 +4864,92 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Axe Kick</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Axe Kick</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>KS GB</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>44e43c47-46ab-4180-823e-3dad4d74904a</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>40f800ab-513b-4013-9dce-31e1bd492968</t>
         </is>
@@ -4937,85 +4973,90 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>f,N,d,df,f+4,4</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>Tsunami Kick</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Tsunami Kick</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>-3 -15</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>-3 -15</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>+8 -4</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>+8 -4</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>+8 -4</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>+8 -4</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>13,18</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>13,18</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>4f672f8e-37fa-4a5d-b50e-c90cb7bf7fc0</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>9e44c578-ed80-4820-ac11-28f086304220</t>
         </is>
@@ -5032,97 +5073,97 @@
           <t>f,N,d,DF+4,4</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Hell Sweeps</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Hell Sweeps</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>-23 -23</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>-23 -23</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>15,12</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>15,12</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>Does 18 damage on a clean hit if only one hell sweep is executed.</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>eaa4baae-faf6-460d-8873-abc9d24e1b90</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>7d06343d-d72d-49eb-8e3d-ca861278fd9d</t>
         </is>
@@ -5139,92 +5180,92 @@
           <t>uf+4,4</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Spinning Demon</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Spinning Demon</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>-26 -20</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>-26 -20</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>25,15</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>25,15</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>hL</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>hL</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>e1a532f6-e86e-4551-8fc7-f36c47666b7a</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>fb72ec9e-67be-46e9-bb84-37862406c96c</t>
         </is>
@@ -5241,57 +5282,57 @@
           <t>4~3</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Demon Scissors</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Demon Scissors</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>9767bef9-ec31-4509-b432-a4ac435b209a</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>6d8e6d74-3e25-4a94-8290-ef352e2f192e</t>
         </is>
@@ -5323,125 +5364,130 @@
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E60" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E60" s="1" t="inlineStr">
+      <c r="F60" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F60" s="1" t="inlineStr">
+      <c r="G60" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G60" s="1" t="inlineStr">
+      <c r="H60" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H60" s="1" t="inlineStr">
+      <c r="I60" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I60" s="1" t="inlineStr">
+      <c r="J60" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J60" s="1" t="inlineStr">
+      <c r="K60" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K60" s="1" t="inlineStr">
+      <c r="L60" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L60" s="1" t="inlineStr">
+      <c r="M60" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M60" s="1" t="inlineStr">
+      <c r="N60" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N60" s="1" t="inlineStr">
+      <c r="O60" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O60" s="1" t="inlineStr">
+      <c r="P60" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P60" s="1" t="inlineStr">
+      <c r="Q60" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q60" s="1" t="inlineStr">
+      <c r="R60" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R60" s="1" t="inlineStr">
+      <c r="S60" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S60" s="1" t="inlineStr">
+      <c r="T60" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T60" s="1" t="inlineStr">
+      <c r="U60" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U60" s="1" t="inlineStr">
+      <c r="V60" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V60" s="1" t="inlineStr">
+      <c r="W60" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W60" s="1" t="inlineStr">
+      <c r="X60" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X60" s="1" t="inlineStr">
+      <c r="Y60" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y60" s="1" t="inlineStr">
+      <c r="Z60" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z60" s="1" t="inlineStr">
+      <c r="AA60" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA60" s="1" t="inlineStr">
+      <c r="AB60" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB60" s="1" t="inlineStr">
+      <c r="AC60" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -5458,77 +5504,77 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Laser Beam</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Laser Beam</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>JG CF</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>Triggers an automatic Windmill Punches with all Jacks. All Jacks will go into a headdive if you try to hit them with a laser during the Windmill or go into the P Jack's Clock Up if you try to hit them with a non laser attack.</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>8382fbfe-1f7c-4fe8-b853-69c763839dee</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>aff79461-3491-43c4-bcc3-7d014a60fb14</t>
         </is>
@@ -5545,72 +5591,72 @@
           <t>u+1+2</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Laser Blast</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Laser Blast</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>Triggers an automatic Windmill Punches with all Jacks. All Jacks will go into a headdive if you try to hit them with a laser during the Windmill or go into the P Jack's Clock Up if you try to hit them with a non laser attack.</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>006d30b8-7ac7-4a9e-a63f-2906b0d49df0</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>3f11a3b2-d050-4b27-a82f-54848c790832</t>
         </is>
@@ -5627,82 +5673,82 @@
           <t>3+4</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Devil Blaster</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Devil Blaster</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>3e018ae8-2b00-48b7-a4b1-20c53d3566fe</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>28e3d669-227d-46ad-9293-fd57b0bf9433</t>
         </is>
@@ -5719,82 +5765,82 @@
           <t>3+4,3+4</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Reverse Devil Blaster</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Reverse Devil Blaster</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>75ea5bfc-8445-4301-bc80-fdfead4f2065</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>57847bbd-495a-40b1-ad71-6986567b169f</t>
         </is>
@@ -5826,125 +5872,130 @@
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E67" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E67" s="1" t="inlineStr">
+      <c r="F67" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F67" s="1" t="inlineStr">
+      <c r="G67" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G67" s="1" t="inlineStr">
+      <c r="H67" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H67" s="1" t="inlineStr">
+      <c r="I67" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I67" s="1" t="inlineStr">
+      <c r="J67" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J67" s="1" t="inlineStr">
+      <c r="K67" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K67" s="1" t="inlineStr">
+      <c r="L67" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L67" s="1" t="inlineStr">
+      <c r="M67" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M67" s="1" t="inlineStr">
+      <c r="N67" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N67" s="1" t="inlineStr">
+      <c r="O67" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O67" s="1" t="inlineStr">
+      <c r="P67" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P67" s="1" t="inlineStr">
+      <c r="Q67" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q67" s="1" t="inlineStr">
+      <c r="R67" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R67" s="1" t="inlineStr">
+      <c r="S67" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S67" s="1" t="inlineStr">
+      <c r="T67" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T67" s="1" t="inlineStr">
+      <c r="U67" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U67" s="1" t="inlineStr">
+      <c r="V67" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V67" s="1" t="inlineStr">
+      <c r="W67" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W67" s="1" t="inlineStr">
+      <c r="X67" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X67" s="1" t="inlineStr">
+      <c r="Y67" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y67" s="1" t="inlineStr">
+      <c r="Z67" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z67" s="1" t="inlineStr">
+      <c r="AA67" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA67" s="1" t="inlineStr">
+      <c r="AB67" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB67" s="1" t="inlineStr">
+      <c r="AC67" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -5961,42 +6012,42 @@
           <t>f,f+2,1,2,2,3,4,4,1,2,1</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>7,8,6,7,6,11,5,5,8,30</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>7,8,6,7,6,11,5,5,8,30</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>hhhhmmLhmm</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>hhhhmmLhmm</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>f5b8d288-963e-48b0-91a0-9547d3e2d9cf</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>f5b8d288-963e-48b0-91a0-9547d3e2d9cf</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
+      <c r="AC68" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
